--- a/metrics/Global_Metrics_Ablation_Study_Naive.xlsx
+++ b/metrics/Global_Metrics_Ablation_Study_Naive.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.691450704317539</v>
+        <v>2.575358234748719</v>
       </c>
       <c r="C2" t="n">
-        <v>2.47840979410485</v>
+        <v>2.260183537706637</v>
       </c>
       <c r="D2" t="n">
-        <v>10.05083869788076</v>
+        <v>9.611631094734744</v>
       </c>
       <c r="E2" t="n">
-        <v>3.170305773562033</v>
+        <v>3.100263068633812</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8739419878356576</v>
+        <v>0.8920448950754428</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9348812624428647</v>
+        <v>0.9446022609532569</v>
       </c>
       <c r="H2" t="n">
-        <v>0.936717967785326</v>
+        <v>0.9454413267844604</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7840163137664763</v>
+        <v>0.8048715206341066</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009066073000837116</v>
+        <v>4.125633956025067</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1203891232489185</v>
+        <v>4.81130088280863</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4691274091986587</v>
+        <v>21.27900720862076</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4706196096815083</v>
+        <v>4.612917429200392</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3901661316616527</v>
+        <v>0.7713915453825121</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1227646283086803</v>
+        <v>0.9637283767485599</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1575039255524298</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9699476330158194</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8743305187417123</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.139007097461058</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.847810854668758</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.4510332852153</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.539888439521567</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9129137720942155</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9619699392425382</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.958125548445609</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8346028479422305</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.271268566554937</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.138491119656399</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.249635171382805</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.692514655741507</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.913707589478421</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9646614317632395</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9652579816935466</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8505353507709221</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02073227994390597</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1972689039305076</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.01060861415895253</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01163616867605044</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.02116228729725567</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1934443892212738</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2225543377813843</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3489016665463387</v>
+        <v>0.3708379882706064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2276309423220937</v>
+        <v>0.2292946459293761</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2471852282411929</v>
+        <v>0.2769355875336005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4971772603822432</v>
+        <v>0.5262466983588596</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9559165059255866</v>
+        <v>0.9558160655229299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9795858511098426</v>
+        <v>0.9808439662892738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831487123615291</v>
+        <v>0.9831850669441811</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8913967252773219</v>
+        <v>0.8920203815933631</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006735619199833787</v>
+        <v>0.2834714788213825</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03735215663943131</v>
+        <v>0.2156921809113934</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4899948454462442</v>
+        <v>0.141524724426777</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4902119397328348</v>
+        <v>0.3761977198585565</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4417289905491784</v>
+        <v>0.9746128559765234</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02737355381267687</v>
+        <v>0.993322516363215</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02624280162792815</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9913289301072626</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9310757615150853</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2478411799438366</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1667022544022461</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1265216031052371</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3556987533085225</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9572094166846759</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9871901952048208</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9841364025717929</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8906508013044759</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.475795811537493</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3733841795995869</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4156784375794055</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6447312909882732</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9402560280183604</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9803846120508471</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9838510332404428</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8949266043968431</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01120805706611888</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.07293978495071879</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004889685146422684</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.00650197709438266</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01697268467653862</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.05020538153157397</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.05222882016968557</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.07049256105437</v>
+        <v>1.055357350042219</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6915114872804641</v>
+        <v>0.6675511963500504</v>
       </c>
       <c r="D4" t="n">
-        <v>2.393119176469845</v>
+        <v>2.490001328653122</v>
       </c>
       <c r="E4" t="n">
-        <v>1.546970968205236</v>
+        <v>1.577973804805746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9622106182348488</v>
+        <v>0.9647788349711834</v>
       </c>
       <c r="G4" t="n">
-        <v>0.981061925924324</v>
+        <v>0.982258269285981</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9792855300483939</v>
+        <v>0.9765139492104485</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8828429044699259</v>
+        <v>0.8807651099842208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004825899601645478</v>
+        <v>1.324649884372081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1035559941703061</v>
+        <v>1.035292361785746</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4917711626513462</v>
+        <v>3.17875592433409</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4876956564947674</v>
+        <v>1.782906594394134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4360863682963311</v>
+        <v>0.9622488480111165</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08391398881638418</v>
+        <v>0.982488532088156</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07544821993749218</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9794332994792423</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.905141762950074</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.229568563480383</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6477093892964778</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.770802025086998</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.941855304879073</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9075847260163518</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9645348333193855</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9563129691124709</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8426610870480852</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.8537699212979067</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5714554012243909</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.477415772015092</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.215489930857139</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9810807545016548</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9908570044017807</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9869989394541745</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9139983649069979</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01090465064483542</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2266988993439963</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.005614650815419509</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.007602633206939713</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.019251279998305</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1615654972056601</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1229371023857828</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
